--- a/StakeholderRegister.xlsx
+++ b/StakeholderRegister.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://temahau-my.sharepoint.com/personal/greenz1_student_eit_ac_nz/Documents/2026/Agile Projects/Android 18 Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{621FD813-90FB-4679-8A23-CB1B5ADAA232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3882EA1F-BF36-4D7B-9BE2-F5B7EE8232C8}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{621FD813-90FB-4679-8A23-CB1B5ADAA232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1A3D738-7961-403A-BA33-FCBDF5828139}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E5E51488-5D09-4234-A39A-72330E0AA533}"/>
   </bookViews>
@@ -123,7 +123,7 @@
     <t>Product Manager</t>
   </si>
   <si>
-    <t>Developer</t>
+    <t>Development</t>
   </si>
 </sst>
 </file>
@@ -316,56 +316,56 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -765,47 +765,47 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="21"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
-      <c r="Z3" s="21"/>
-      <c r="AA3" s="21"/>
-      <c r="AB3" s="21"/>
-      <c r="AC3" s="21"/>
-      <c r="AD3" s="21"/>
-      <c r="AE3" s="21"/>
-      <c r="AF3" s="21"/>
-      <c r="AG3" s="21"/>
-      <c r="AH3" s="21"/>
-      <c r="AI3" s="21"/>
-      <c r="AJ3" s="21"/>
-      <c r="AK3" s="21"/>
-      <c r="AL3" s="21"/>
-      <c r="AM3" s="21"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="11"/>
+      <c r="AA3" s="11"/>
+      <c r="AB3" s="11"/>
+      <c r="AC3" s="11"/>
+      <c r="AD3" s="11"/>
+      <c r="AE3" s="11"/>
+      <c r="AF3" s="11"/>
+      <c r="AG3" s="11"/>
+      <c r="AH3" s="11"/>
+      <c r="AI3" s="11"/>
+      <c r="AJ3" s="11"/>
+      <c r="AK3" s="11"/>
+      <c r="AL3" s="11"/>
+      <c r="AM3" s="11"/>
     </row>
     <row r="4" spans="1:39" ht="18.75" x14ac:dyDescent="0.3">
       <c r="H4" s="2"/>
@@ -821,50 +821,50 @@
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="16" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="16" t="s">
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
       <c r="O6" s="1"/>
       <c r="S6" s="10"/>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="18" t="s">
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18" t="s">
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="C8" s="5"/>
@@ -879,545 +879,545 @@
       <c r="A9" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
       <c r="F9" s="9"/>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="20" t="s">
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="19" t="s">
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19" t="s">
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="T9" s="19"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19" t="s">
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="23"/>
+      <c r="W9" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="19" t="s">
+      <c r="X9" s="23"/>
+      <c r="Y9" s="23"/>
+      <c r="Z9" s="23"/>
+      <c r="AA9" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="AB9" s="19"/>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="19"/>
+      <c r="AB9" s="23"/>
+      <c r="AC9" s="23"/>
+      <c r="AD9" s="23"/>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
       <c r="F10" s="6"/>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="12" t="s">
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="11" t="s">
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11" t="s">
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="11" t="s">
+      <c r="T10" s="24"/>
+      <c r="U10" s="24"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="11"/>
-      <c r="Z10" s="11"/>
-      <c r="AA10" s="15" t="s">
+      <c r="X10" s="24"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="11"/>
-      <c r="AD10" s="11"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="24"/>
+      <c r="AD10" s="24"/>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="14" t="s">
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="13" t="s">
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13" t="s">
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="13" t="s">
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="12"/>
+      <c r="W11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13"/>
+      <c r="X11" s="12"/>
+      <c r="Y11" s="12"/>
+      <c r="Z11" s="12"/>
       <c r="AA11" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="13"/>
+      <c r="AB11" s="12"/>
+      <c r="AC11" s="12"/>
+      <c r="AD11" s="12"/>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
       <c r="F12" s="6"/>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="12" t="s">
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="11" t="s">
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11" t="s">
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11" t="s">
+      <c r="T12" s="24"/>
+      <c r="U12" s="24"/>
+      <c r="V12" s="24"/>
+      <c r="W12" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="11"/>
-      <c r="Z12" s="11"/>
-      <c r="AA12" s="15" t="s">
+      <c r="X12" s="24"/>
+      <c r="Y12" s="24"/>
+      <c r="Z12" s="24"/>
+      <c r="AA12" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="11"/>
-      <c r="AD12" s="11"/>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="24"/>
+      <c r="AD12" s="24"/>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="13"/>
-      <c r="U13" s="13"/>
-      <c r="V13" s="13"/>
-      <c r="W13" s="13"/>
-      <c r="X13" s="13"/>
-      <c r="Y13" s="13"/>
-      <c r="Z13" s="13"/>
-      <c r="AA13" s="13"/>
-      <c r="AB13" s="13"/>
-      <c r="AC13" s="13"/>
-      <c r="AD13" s="13"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="12"/>
+      <c r="V13" s="12"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="12"/>
+      <c r="AA13" s="12"/>
+      <c r="AB13" s="12"/>
+      <c r="AC13" s="12"/>
+      <c r="AD13" s="12"/>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
       <c r="F14" s="6"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="11"/>
-      <c r="Z14" s="11"/>
-      <c r="AA14" s="11"/>
-      <c r="AB14" s="11"/>
-      <c r="AC14" s="11"/>
-      <c r="AD14" s="11"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="24"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="24"/>
+      <c r="AD14" s="24"/>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="13"/>
-      <c r="Z15" s="13"/>
-      <c r="AA15" s="13"/>
-      <c r="AB15" s="13"/>
-      <c r="AC15" s="13"/>
-      <c r="AD15" s="13"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="12"/>
+      <c r="AA15" s="12"/>
+      <c r="AB15" s="12"/>
+      <c r="AC15" s="12"/>
+      <c r="AD15" s="12"/>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
       <c r="F16" s="6"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="11"/>
-      <c r="Z16" s="11"/>
-      <c r="AA16" s="11"/>
-      <c r="AB16" s="11"/>
-      <c r="AC16" s="11"/>
-      <c r="AD16" s="11"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="24"/>
+      <c r="V16" s="24"/>
+      <c r="W16" s="24"/>
+      <c r="X16" s="24"/>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="24"/>
+      <c r="AD16" s="24"/>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="13"/>
-      <c r="AA17" s="13"/>
-      <c r="AB17" s="13"/>
-      <c r="AC17" s="13"/>
-      <c r="AD17" s="13"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="12"/>
+      <c r="U17" s="12"/>
+      <c r="V17" s="12"/>
+      <c r="W17" s="12"/>
+      <c r="X17" s="12"/>
+      <c r="Y17" s="12"/>
+      <c r="Z17" s="12"/>
+      <c r="AA17" s="12"/>
+      <c r="AB17" s="12"/>
+      <c r="AC17" s="12"/>
+      <c r="AD17" s="12"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
       <c r="F18" s="6"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="11"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="11"/>
-      <c r="Z18" s="11"/>
-      <c r="AA18" s="11"/>
-      <c r="AB18" s="11"/>
-      <c r="AC18" s="11"/>
-      <c r="AD18" s="11"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
+      <c r="S18" s="24"/>
+      <c r="T18" s="24"/>
+      <c r="U18" s="24"/>
+      <c r="V18" s="24"/>
+      <c r="W18" s="24"/>
+      <c r="X18" s="24"/>
+      <c r="Y18" s="24"/>
+      <c r="Z18" s="24"/>
+      <c r="AA18" s="24"/>
+      <c r="AB18" s="24"/>
+      <c r="AC18" s="24"/>
+      <c r="AD18" s="24"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
-      <c r="U19" s="13"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="13"/>
-      <c r="X19" s="13"/>
-      <c r="Y19" s="13"/>
-      <c r="Z19" s="13"/>
-      <c r="AA19" s="13"/>
-      <c r="AB19" s="13"/>
-      <c r="AC19" s="13"/>
-      <c r="AD19" s="13"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
+      <c r="U19" s="12"/>
+      <c r="V19" s="12"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="12"/>
+      <c r="Y19" s="12"/>
+      <c r="Z19" s="12"/>
+      <c r="AA19" s="12"/>
+      <c r="AB19" s="12"/>
+      <c r="AC19" s="12"/>
+      <c r="AD19" s="12"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
       <c r="F20" s="6"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="11"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="11"/>
-      <c r="Z20" s="11"/>
-      <c r="AA20" s="11"/>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="11"/>
-      <c r="AD20" s="11"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
+      <c r="S20" s="24"/>
+      <c r="T20" s="24"/>
+      <c r="U20" s="24"/>
+      <c r="V20" s="24"/>
+      <c r="W20" s="24"/>
+      <c r="X20" s="24"/>
+      <c r="Y20" s="24"/>
+      <c r="Z20" s="24"/>
+      <c r="AA20" s="24"/>
+      <c r="AB20" s="24"/>
+      <c r="AC20" s="24"/>
+      <c r="AD20" s="24"/>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
       <c r="F21" s="7"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="13"/>
-      <c r="U21" s="13"/>
-      <c r="V21" s="13"/>
-      <c r="W21" s="13"/>
-      <c r="X21" s="13"/>
-      <c r="Y21" s="13"/>
-      <c r="Z21" s="13"/>
-      <c r="AA21" s="13"/>
-      <c r="AB21" s="13"/>
-      <c r="AC21" s="13"/>
-      <c r="AD21" s="13"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
+      <c r="Z21" s="12"/>
+      <c r="AA21" s="12"/>
+      <c r="AB21" s="12"/>
+      <c r="AC21" s="12"/>
+      <c r="AD21" s="12"/>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
       <c r="F22" s="6"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
-      <c r="S22" s="11"/>
-      <c r="T22" s="11"/>
-      <c r="U22" s="11"/>
-      <c r="V22" s="11"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="11"/>
-      <c r="Z22" s="11"/>
-      <c r="AA22" s="11"/>
-      <c r="AB22" s="11"/>
-      <c r="AC22" s="11"/>
-      <c r="AD22" s="11"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
+      <c r="S22" s="24"/>
+      <c r="T22" s="24"/>
+      <c r="U22" s="24"/>
+      <c r="V22" s="24"/>
+      <c r="W22" s="24"/>
+      <c r="X22" s="24"/>
+      <c r="Y22" s="24"/>
+      <c r="Z22" s="24"/>
+      <c r="AA22" s="24"/>
+      <c r="AB22" s="24"/>
+      <c r="AC22" s="24"/>
+      <c r="AD22" s="24"/>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="13"/>
-      <c r="T23" s="13"/>
-      <c r="U23" s="13"/>
-      <c r="V23" s="13"/>
-      <c r="W23" s="13"/>
-      <c r="X23" s="13"/>
-      <c r="Y23" s="13"/>
-      <c r="Z23" s="13"/>
-      <c r="AA23" s="13"/>
-      <c r="AB23" s="13"/>
-      <c r="AC23" s="13"/>
-      <c r="AD23" s="13"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="12"/>
+      <c r="U23" s="12"/>
+      <c r="V23" s="12"/>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="12"/>
+      <c r="Z23" s="12"/>
+      <c r="AA23" s="12"/>
+      <c r="AB23" s="12"/>
+      <c r="AC23" s="12"/>
+      <c r="AD23" s="12"/>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -1445,6 +1445,94 @@
     </row>
   </sheetData>
   <mergeCells count="112">
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="S22:V22"/>
+    <mergeCell ref="W22:Z22"/>
+    <mergeCell ref="AA22:AD22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="S23:V23"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="AA23:AD23"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="S19:V19"/>
+    <mergeCell ref="W19:Z19"/>
+    <mergeCell ref="AA19:AD19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="S20:V20"/>
+    <mergeCell ref="W20:Z20"/>
+    <mergeCell ref="AA20:AD20"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="S17:V17"/>
+    <mergeCell ref="W17:Z17"/>
+    <mergeCell ref="AA17:AD17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="O18:R18"/>
+    <mergeCell ref="S18:V18"/>
+    <mergeCell ref="W18:Z18"/>
+    <mergeCell ref="AA18:AD18"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="S15:V15"/>
+    <mergeCell ref="W15:Z15"/>
+    <mergeCell ref="AA15:AD15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:V16"/>
+    <mergeCell ref="W16:Z16"/>
+    <mergeCell ref="AA16:AD16"/>
+    <mergeCell ref="K13:N13"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="S13:V13"/>
+    <mergeCell ref="W13:Z13"/>
+    <mergeCell ref="AA13:AD13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="S14:V14"/>
+    <mergeCell ref="W14:Z14"/>
+    <mergeCell ref="AA14:AD14"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="S11:V11"/>
+    <mergeCell ref="W11:Z11"/>
+    <mergeCell ref="AA11:AD11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="S12:V12"/>
+    <mergeCell ref="W12:Z12"/>
+    <mergeCell ref="AA12:AD12"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="S10:V10"/>
+    <mergeCell ref="W10:Z10"/>
+    <mergeCell ref="AA10:AD10"/>
+    <mergeCell ref="J6:N6"/>
+    <mergeCell ref="J7:N7"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="S9:V9"/>
+    <mergeCell ref="W9:Z9"/>
     <mergeCell ref="A3:AM3"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="G21:J21"/>
@@ -1469,94 +1557,6 @@
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="AA9:AD9"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="S10:V10"/>
-    <mergeCell ref="W10:Z10"/>
-    <mergeCell ref="AA10:AD10"/>
-    <mergeCell ref="J6:N6"/>
-    <mergeCell ref="J7:N7"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="S9:V9"/>
-    <mergeCell ref="W9:Z9"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="S11:V11"/>
-    <mergeCell ref="W11:Z11"/>
-    <mergeCell ref="AA11:AD11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="S12:V12"/>
-    <mergeCell ref="W12:Z12"/>
-    <mergeCell ref="AA12:AD12"/>
-    <mergeCell ref="K13:N13"/>
-    <mergeCell ref="O13:R13"/>
-    <mergeCell ref="S13:V13"/>
-    <mergeCell ref="W13:Z13"/>
-    <mergeCell ref="AA13:AD13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="S14:V14"/>
-    <mergeCell ref="W14:Z14"/>
-    <mergeCell ref="AA14:AD14"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="S15:V15"/>
-    <mergeCell ref="W15:Z15"/>
-    <mergeCell ref="AA15:AD15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:V16"/>
-    <mergeCell ref="W16:Z16"/>
-    <mergeCell ref="AA16:AD16"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="O17:R17"/>
-    <mergeCell ref="S17:V17"/>
-    <mergeCell ref="W17:Z17"/>
-    <mergeCell ref="AA17:AD17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="S18:V18"/>
-    <mergeCell ref="W18:Z18"/>
-    <mergeCell ref="AA18:AD18"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="S19:V19"/>
-    <mergeCell ref="W19:Z19"/>
-    <mergeCell ref="AA19:AD19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="K20:N20"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="S20:V20"/>
-    <mergeCell ref="W20:Z20"/>
-    <mergeCell ref="AA20:AD20"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="S22:V22"/>
-    <mergeCell ref="W22:Z22"/>
-    <mergeCell ref="AA22:AD22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="S23:V23"/>
-    <mergeCell ref="W23:Z23"/>
-    <mergeCell ref="AA23:AD23"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="2">
